--- a/public/templates/reporte_almacen_combustible_distribucion.xlsx
+++ b/public/templates/reporte_almacen_combustible_distribucion.xlsx
@@ -1,35 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\santarita\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\tierrasanta\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318B1363-8E13-4B0C-9DB3-B70DA84FDFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830DF4EA-235C-4215-9473-27016860AC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DISTRIBUCION" sheetId="1" r:id="rId1"/>
+    <sheet name="DISTRIBUCION" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DISTRIBUCION!$A$1:$M$61</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>01/2025/2025</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t xml:space="preserve">FECHA </t>
   </si>
@@ -68,6 +59,24 @@
   </si>
   <si>
     <t>VALOR Y/O COSTO</t>
+  </si>
+  <si>
+    <t>REPORTE DE LA DISTRIBUCIÓN DE COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>AÑO:</t>
+  </si>
+  <si>
+    <t>MES:</t>
+  </si>
+  <si>
+    <t>COMBUSTIBLE:</t>
+  </si>
+  <si>
+    <t>MAQUINARIA:</t>
+  </si>
+  <si>
+    <t>SIN FILTRO</t>
   </si>
 </sst>
 </file>
@@ -98,14 +107,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -143,6 +144,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -158,7 +167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -166,56 +175,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="18" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -223,13 +195,13 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -238,28 +210,27 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="18" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -268,7 +239,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -277,13 +248,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -301,6 +276,28 @@
         <vertAlign val="baseline"/>
         <sz val="9"/>
       </font>
+      <numFmt numFmtId="167" formatCode="dd\-mmm"/>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
       <alignment horizontal="right" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -429,27 +426,6 @@
         <vertAlign val="baseline"/>
         <sz val="9"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-      </font>
-      <numFmt numFmtId="21" formatCode="dd\-mmm"/>
     </dxf>
     <dxf>
       <font>
@@ -475,22 +451,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="DistribucionTable" ref="A3:M4" insertRow="1" dataDxfId="13">
-  <autoFilter ref="A3:M4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EC38CE79-D354-47C6-BD81-03371000F251}" name="DistribucionTable" displayName="DistribucionTable" ref="A8:M9" insertRow="1" dataDxfId="13">
+  <autoFilter ref="A8:M9" xr:uid="{EC38CE79-D354-47C6-BD81-03371000F251}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="FECHA " dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="TIEMPO LABOR" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="HORA SALIDA" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TOTAL HORAS" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="CAMPO" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CANT. COMBUSTIBLE" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="COST. COMBUSTIBLE" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="INGRESO" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="LABOR" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="MAQUINARIA" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="PRECIO" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="RATIO" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="VALOR Y/O COSTO" dataDxfId="0" dataCellStyle="Moneda"/>
+    <tableColumn id="1" xr3:uid="{BA4271D9-4BCA-4B1E-A90D-192BF353337D}" name="FECHA " dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{FD3ADDBD-0A04-47CA-B189-653EADF01AF0}" name="TIEMPO LABOR" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{9687E5A0-16C2-4330-8789-D0C01EFE48F8}" name="HORA SALIDA" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{B1C6AEB4-5D75-4324-A894-B4E2C9D4A644}" name="TOTAL HORAS" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{B192227A-108E-49A5-B8E0-7FBFBA70E7C3}" name="CAMPO" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{C8517740-9009-4F4A-8AAC-C4B61E90373B}" name="CANT. COMBUSTIBLE" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{BAE6E021-E9D8-4833-8783-2054C400F8BE}" name="COST. COMBUSTIBLE" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{B43221CB-95A1-46D9-8C68-377D27903CB6}" name="INGRESO" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{D07DF8C4-B02A-4B43-9960-D04A0D747705}" name="LABOR" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{E6B57FF5-64AA-473E-83E0-4960BFE0FAB9}" name="MAQUINARIA" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{B9D5B66B-0D12-4005-B1A4-993E95CB1CE9}" name="PRECIO" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{1EED6BD0-2F58-466E-B6CD-127C45463C07}" name="RATIO" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{9AFE37CB-4F8D-44D2-AA63-BA712FFD3A6E}" name="VALOR Y/O COSTO" dataDxfId="2" dataCellStyle="Moneda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -816,257 +792,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:EQ4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12A9062-E597-455B-8D1C-CCB858642E3E}">
+  <dimension ref="A1:EQ9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="9" customWidth="1"/>
-    <col min="2" max="3" width="9.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="21" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" style="27" customWidth="1"/>
-    <col min="9" max="9" width="24.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="21" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" style="7" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="26" customWidth="1"/>
+    <col min="9" max="9" width="24.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.44140625" style="20" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" style="22" customWidth="1"/>
+    <col min="14" max="14" width="7.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+    </row>
+    <row r="2" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:147" s="8" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="30"/>
+      <c r="B8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:147" x14ac:dyDescent="0.25">
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:147" s="8" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:147" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="1"/>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="1"/>
-      <c r="AR4" s="1"/>
-      <c r="AS4" s="1"/>
-      <c r="AT4" s="1"/>
-      <c r="AU4" s="1"/>
-      <c r="AV4" s="1"/>
-      <c r="AW4" s="1"/>
-      <c r="AX4" s="1"/>
-      <c r="AY4" s="1"/>
-      <c r="AZ4" s="1"/>
-      <c r="BA4" s="1"/>
-      <c r="BB4" s="1"/>
-      <c r="BC4" s="1"/>
-      <c r="BD4" s="1"/>
-      <c r="BE4" s="1"/>
-      <c r="BF4" s="1"/>
-      <c r="BG4" s="1"/>
-      <c r="BH4" s="1"/>
-      <c r="BI4" s="1"/>
-      <c r="BJ4" s="1"/>
-      <c r="BK4" s="1"/>
-      <c r="BL4" s="1"/>
-      <c r="BM4" s="1"/>
-      <c r="BN4" s="1"/>
-      <c r="BO4" s="1"/>
-      <c r="BP4" s="1"/>
-      <c r="BQ4" s="1"/>
-      <c r="BR4" s="1"/>
-      <c r="BS4" s="1"/>
-      <c r="BT4" s="1"/>
-      <c r="BU4" s="1"/>
-      <c r="BV4" s="1"/>
-      <c r="BW4" s="1"/>
-      <c r="BX4" s="1"/>
-      <c r="BY4" s="1"/>
-      <c r="BZ4" s="1"/>
-      <c r="CA4" s="1"/>
-      <c r="CB4" s="1"/>
-      <c r="CC4" s="1"/>
-      <c r="CD4" s="1"/>
-      <c r="CE4" s="1"/>
-      <c r="CF4" s="1"/>
-      <c r="CG4" s="1"/>
-      <c r="CH4" s="1"/>
-      <c r="CI4" s="1"/>
-      <c r="CJ4" s="1"/>
-      <c r="CK4" s="1"/>
-      <c r="CL4" s="1"/>
-      <c r="CM4" s="1"/>
-      <c r="CN4" s="1"/>
-      <c r="CO4" s="1"/>
-      <c r="CP4" s="1"/>
-      <c r="CQ4" s="1"/>
-      <c r="CR4" s="1"/>
-      <c r="CS4" s="1"/>
-      <c r="CT4" s="1"/>
-      <c r="CU4" s="1"/>
-      <c r="CV4" s="1"/>
-      <c r="CW4" s="1"/>
-      <c r="CX4" s="1"/>
-      <c r="CY4" s="1"/>
-      <c r="CZ4" s="1"/>
-      <c r="DA4" s="1"/>
-      <c r="DB4" s="1"/>
-      <c r="DC4" s="1"/>
-      <c r="DD4" s="1"/>
-      <c r="DE4" s="1"/>
-      <c r="DF4" s="1"/>
-      <c r="DG4" s="1"/>
-      <c r="DH4" s="1"/>
-      <c r="DI4" s="1"/>
-      <c r="DJ4" s="1"/>
-      <c r="DK4" s="1"/>
-      <c r="DL4" s="1"/>
-      <c r="DM4" s="1"/>
-      <c r="DN4" s="1"/>
-      <c r="DO4" s="1"/>
-      <c r="DP4" s="1"/>
-      <c r="DQ4" s="1"/>
-      <c r="DR4" s="1"/>
-      <c r="DS4" s="1"/>
-      <c r="DT4" s="1"/>
-      <c r="DU4" s="1"/>
-      <c r="DV4" s="1"/>
-      <c r="DW4" s="1"/>
-      <c r="DX4" s="1"/>
-      <c r="DY4" s="1"/>
-      <c r="DZ4" s="1"/>
-      <c r="EA4" s="1"/>
-      <c r="EB4" s="1"/>
-      <c r="EC4" s="1"/>
-      <c r="ED4" s="1"/>
-      <c r="EE4" s="1"/>
-      <c r="EF4" s="1"/>
-      <c r="EG4" s="1"/>
-      <c r="EH4" s="1"/>
-      <c r="EI4" s="1"/>
-      <c r="EJ4" s="1"/>
-      <c r="EK4" s="1"/>
-      <c r="EL4" s="1"/>
-      <c r="EM4" s="1"/>
-      <c r="EN4" s="1"/>
-      <c r="EO4" s="1"/>
-      <c r="EP4" s="1"/>
-      <c r="EQ4" s="1"/>
+    <row r="9" spans="1:147" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A9" s="31"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="1"/>
+      <c r="AO9" s="1"/>
+      <c r="AP9" s="1"/>
+      <c r="AQ9" s="1"/>
+      <c r="AR9" s="1"/>
+      <c r="AS9" s="1"/>
+      <c r="AT9" s="1"/>
+      <c r="AU9" s="1"/>
+      <c r="AV9" s="1"/>
+      <c r="AW9" s="1"/>
+      <c r="AX9" s="1"/>
+      <c r="AY9" s="1"/>
+      <c r="AZ9" s="1"/>
+      <c r="BA9" s="1"/>
+      <c r="BB9" s="1"/>
+      <c r="BC9" s="1"/>
+      <c r="BD9" s="1"/>
+      <c r="BE9" s="1"/>
+      <c r="BF9" s="1"/>
+      <c r="BG9" s="1"/>
+      <c r="BH9" s="1"/>
+      <c r="BI9" s="1"/>
+      <c r="BJ9" s="1"/>
+      <c r="BK9" s="1"/>
+      <c r="BL9" s="1"/>
+      <c r="BM9" s="1"/>
+      <c r="BN9" s="1"/>
+      <c r="BO9" s="1"/>
+      <c r="BP9" s="1"/>
+      <c r="BQ9" s="1"/>
+      <c r="BR9" s="1"/>
+      <c r="BS9" s="1"/>
+      <c r="BT9" s="1"/>
+      <c r="BU9" s="1"/>
+      <c r="BV9" s="1"/>
+      <c r="BW9" s="1"/>
+      <c r="BX9" s="1"/>
+      <c r="BY9" s="1"/>
+      <c r="BZ9" s="1"/>
+      <c r="CA9" s="1"/>
+      <c r="CB9" s="1"/>
+      <c r="CC9" s="1"/>
+      <c r="CD9" s="1"/>
+      <c r="CE9" s="1"/>
+      <c r="CF9" s="1"/>
+      <c r="CG9" s="1"/>
+      <c r="CH9" s="1"/>
+      <c r="CI9" s="1"/>
+      <c r="CJ9" s="1"/>
+      <c r="CK9" s="1"/>
+      <c r="CL9" s="1"/>
+      <c r="CM9" s="1"/>
+      <c r="CN9" s="1"/>
+      <c r="CO9" s="1"/>
+      <c r="CP9" s="1"/>
+      <c r="CQ9" s="1"/>
+      <c r="CR9" s="1"/>
+      <c r="CS9" s="1"/>
+      <c r="CT9" s="1"/>
+      <c r="CU9" s="1"/>
+      <c r="CV9" s="1"/>
+      <c r="CW9" s="1"/>
+      <c r="CX9" s="1"/>
+      <c r="CY9" s="1"/>
+      <c r="CZ9" s="1"/>
+      <c r="DA9" s="1"/>
+      <c r="DB9" s="1"/>
+      <c r="DC9" s="1"/>
+      <c r="DD9" s="1"/>
+      <c r="DE9" s="1"/>
+      <c r="DF9" s="1"/>
+      <c r="DG9" s="1"/>
+      <c r="DH9" s="1"/>
+      <c r="DI9" s="1"/>
+      <c r="DJ9" s="1"/>
+      <c r="DK9" s="1"/>
+      <c r="DL9" s="1"/>
+      <c r="DM9" s="1"/>
+      <c r="DN9" s="1"/>
+      <c r="DO9" s="1"/>
+      <c r="DP9" s="1"/>
+      <c r="DQ9" s="1"/>
+      <c r="DR9" s="1"/>
+      <c r="DS9" s="1"/>
+      <c r="DT9" s="1"/>
+      <c r="DU9" s="1"/>
+      <c r="DV9" s="1"/>
+      <c r="DW9" s="1"/>
+      <c r="DX9" s="1"/>
+      <c r="DY9" s="1"/>
+      <c r="DZ9" s="1"/>
+      <c r="EA9" s="1"/>
+      <c r="EB9" s="1"/>
+      <c r="EC9" s="1"/>
+      <c r="ED9" s="1"/>
+      <c r="EE9" s="1"/>
+      <c r="EF9" s="1"/>
+      <c r="EG9" s="1"/>
+      <c r="EH9" s="1"/>
+      <c r="EI9" s="1"/>
+      <c r="EJ9" s="1"/>
+      <c r="EK9" s="1"/>
+      <c r="EL9" s="1"/>
+      <c r="EM9" s="1"/>
+      <c r="EN9" s="1"/>
+      <c r="EO9" s="1"/>
+      <c r="EP9" s="1"/>
+      <c r="EQ9" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{5C01C179-EC2F-4148-93B9-A01333C49EEE}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E9" xr:uid="{4C157442-5EFD-4D1A-BA9D-CD0F1492FD0B}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{9B52D6A5-1C77-4090-BCD9-06F7414DA093}">
       <formula1>0</formula1>
       <formula2>24</formula2>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{47D8697D-BDF7-4BDF-9360-FB02FFEE651E}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="285" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="285" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
